--- a/docs/Sundial_Service_Call_Fields_by_Section.xlsx
+++ b/docs/Sundial_Service_Call_Fields_by_Section.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -791,12 +791,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Picklist: Scheduled / En Route / In Progress / Complete / Cancelled / No-Show (default Scheduled)</t>
+          <t>Picklist: Unscheduled / Scheduled / En Route / In Progress / Complete / Cancelled / No-Show (default Scheduled)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>En Route = 'on my way' (texts the customer when notify is on; ends the previous call's clock and starts drive time on this one).</t>
+          <t>Unscheduled = created without a window (sits in the dispatch tray until dropped on the board; 2026-09-15). En Route = 'on my way' (texts the customer when notify is on; ends the previous call's clock and starts drive time on this one).</t>
         </is>
       </c>
     </row>
@@ -1217,6 +1217,87 @@
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Count of photos at SUNDIAL/{jobId}/photos/{callId}/ (metadata-derived).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Billable to Customer</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Billable_to_Customer__c</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Checkbox (default false)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Office opt-in: bill this call's hours to the customer as a Labor line on the estimate (Source = Time). Off = the hours never reach the invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Billable Hours</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Billable_Hours__c</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Number(6,2)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Hours billed. Blank = derived from the clock (Duration Minutes, else Actual Start-&gt;End) rounded UP to the quarter hour; the office may overtype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bill Rate</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Bill_Rate__c</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Currency(16,2)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Hourly rate billed for this call. Blank = the tech's Hourly Bill Rate on Sundial_User__c at billing time; the office may overtype per call or apply one rate to every call on the job.</t>
         </is>
       </c>
     </row>
